--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/17_managed_services_scope.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/17_managed_services_scope.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rddba9ec918b04955"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R1018b69b73c84c07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R5c721501e2d440de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rcccec2f869ca45d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R8d76ece21ee34ea2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R14e6fadfd65148cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rafcd68593a8d4b18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R20d24b9051744592"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R9bcbc6aaafb84723"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rf7483e10340e44fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R258d62403d2044b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R3d9f470238d34d82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -674,7 +674,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ce961bc3edc4c6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf72db9c9cf894676"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -845,7 +845,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N6" s="81" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Executive Office support and managed service scope (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for managed services scope.</x:v>
       </x:c>
       <x:c r="O6" s="82" t="str">
         <x:v>Medium</x:v>
@@ -892,7 +892,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N7" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm Retail Deposits and Branch Operations support and managed service scope (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this managed services scope record is used downstream.</x:v>
       </x:c>
       <x:c r="O7" t="str">
         <x:v>Medium</x:v>
@@ -939,7 +939,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Attach client evidence for Commercial Lending and Treasury support and managed service scope (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O8" t="str">
         <x:v>Medium</x:v>
@@ -986,7 +986,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Reconcile Cards Operations support and managed service scope (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O9" t="str">
         <x:v>Medium</x:v>
@@ -1033,7 +1033,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Operations support and managed service scope (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O10" t="str">
         <x:v>Medium</x:v>
@@ -1080,7 +1080,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Consumer Lending Operations support and managed service scope (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for managed services scope.</x:v>
       </x:c>
       <x:c r="O11" t="str">
         <x:v>Medium</x:v>
@@ -1127,7 +1127,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm Wealth Advisory and Brokerage support and managed service scope (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this managed services scope record is used downstream.</x:v>
       </x:c>
       <x:c r="O12" t="str">
         <x:v>Medium</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Fraud and Risk Operations support and managed service scope (record 8) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O13" t="str">
         <x:v>Medium</x:v>
@@ -1221,7 +1221,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Reconcile Compliance and Model Risk Management support and managed service scope (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O14" t="str">
         <x:v>Medium</x:v>
@@ -1268,7 +1268,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center and Servicing support and managed service scope (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O15" t="str">
         <x:v>Medium</x:v>
@@ -1315,7 +1315,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Digital Account Opening and Onboarding support and managed service scope (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for managed services scope.</x:v>
       </x:c>
       <x:c r="O16" t="str">
         <x:v>Medium</x:v>
@@ -1362,7 +1362,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm Core Banking Modernization support and managed service scope (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this managed services scope record is used downstream.</x:v>
       </x:c>
       <x:c r="O17" t="str">
         <x:v>Medium</x:v>
@@ -1409,7 +1409,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Attach client evidence for Customer 360 Data Product support and managed service scope (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O18" t="str">
         <x:v>Medium</x:v>
@@ -1456,7 +1456,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Reconcile Retail Banking Analytics support and managed service scope (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O19" t="str">
         <x:v>Medium</x:v>
@@ -1503,7 +1503,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics support and managed service scope (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O20" t="str">
         <x:v>Medium</x:v>
@@ -1550,7 +1550,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Payments and Settlement Analytics support and managed service scope (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for managed services scope.</x:v>
       </x:c>
       <x:c r="O21" t="str">
         <x:v>Medium</x:v>
@@ -1597,7 +1597,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Fraud and Risk Analytics support and managed service scope (record 17) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O22" t="str">
         <x:v>Medium</x:v>
@@ -1644,7 +1644,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Attach client evidence for Cloud Data Platform support and managed service scope (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O23" t="str">
         <x:v>Medium</x:v>
@@ -1691,7 +1691,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline support and managed service scope (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O24" t="str">
         <x:v>Medium</x:v>
@@ -1738,7 +1738,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization support and managed service scope (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O25" t="str">
         <x:v>Medium</x:v>
@@ -1785,7 +1785,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Infrastructure and CMDB support and managed service scope (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for managed services scope.</x:v>
       </x:c>
       <x:c r="O26" t="str">
         <x:v>Medium</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm Incident Problem Change Operations support and managed service scope (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this managed services scope record is used downstream.</x:v>
       </x:c>
       <x:c r="O27" t="str">
         <x:v>Medium</x:v>
@@ -1853,7 +1853,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ecdc47018574da0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c83336165794ae0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1928,7 +1928,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7ba3d9ff2134787"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f8877055aeb4aed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2065,7 +2065,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re76eaf416f2d4281"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4984c25677eb4aea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2127,7 +2127,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd400dd91faf45fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R055b5c12f34c419c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2237,7 +2237,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R263e41695d0f416a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a9c87861c084ad1"/>
   </x:tableParts>
 </x:worksheet>
 </file>